--- a/shroom_shop/dried.xlsx
+++ b/shroom_shop/dried.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AnreX\projects\_shrooms\shroom_shop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313A89FC-29DD-4176-84DA-CB5D66997FDA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3A9C09-CF44-4C8F-949C-08B370A65478}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Manual" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Items!$A$1:$X$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Items!$A$1:$Y$172</definedName>
     <definedName name="characteristic_116713_1">Items!$K$1</definedName>
     <definedName name="characteristic_116714_1">Items!$J$1</definedName>
     <definedName name="characteristic_126208_1">Items!$R$1</definedName>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="711">
   <si>
     <t>Subject</t>
   </si>
@@ -2552,10 +2552,13 @@
     <t>лисички;моховики</t>
   </si>
   <si>
+    <t>Подосиновик;Белый гриб;Подберезовик</t>
+  </si>
+  <si>
     <t>моховики;опята</t>
   </si>
   <si>
-    <t>Подосиновик</t>
+    <t>маслята;Белые грибы,подосиновики,подберезовики</t>
   </si>
 </sst>
 </file>
@@ -2877,7 +2880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2944,6 +2947,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -7400,7 +7406,7 @@
       <c r="B59" t="s">
         <v>269</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="24" t="s">
         <v>267</v>
       </c>
       <c r="D59" t="s">
@@ -7428,7 +7434,7 @@
         <v>54</v>
       </c>
       <c r="L59" t="s">
-        <v>207</v>
+        <v>710</v>
       </c>
       <c r="M59" t="s">
         <v>689</v>
@@ -7462,7 +7468,7 @@
       <c r="B60" t="s">
         <v>274</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="24" t="s">
         <v>271</v>
       </c>
       <c r="D60" t="s">
@@ -7490,7 +7496,7 @@
         <v>54</v>
       </c>
       <c r="L60" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M60" t="s">
         <v>689</v>
@@ -14342,7 +14348,7 @@
         <v>173</v>
       </c>
       <c r="L153" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M153" t="s">
         <v>689</v>
@@ -16612,7 +16618,7 @@
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:X172" xr:uid="{43F09F6E-37AA-4DE9-8AC5-C7FE9DDE5298}"/>
+  <autoFilter ref="A1:Y172" xr:uid="{580F052F-B302-4F2D-B6B1-5043EE739040}"/>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" sqref="T2:X5000 N2:Q5000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>-9223372036854770000</formula1>
@@ -16639,16 +16645,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -16669,16 +16675,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -16699,16 +16705,16 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -16729,16 +16735,16 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -16759,16 +16765,16 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -16789,16 +16795,16 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -16819,16 +16825,16 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -17029,14 +17035,14 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -17085,16 +17091,16 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -17115,16 +17121,16 @@
       <c r="Z15" s="2"/>
     </row>
     <row r="16" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -17145,16 +17151,16 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -17175,16 +17181,16 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -17205,16 +17211,16 @@
       <c r="Z18" s="2"/>
     </row>
     <row r="19" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -17235,16 +17241,16 @@
       <c r="Z19" s="2"/>
     </row>
     <row r="20" spans="1:26" ht="102" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
